--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650285</v>
+        <v>121650414</v>
       </c>
       <c r="B2" t="n">
-        <v>57535</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593479</v>
+        <v>593438</v>
       </c>
       <c r="R2" t="n">
-        <v>6722986</v>
+        <v>6722918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650414</v>
+        <v>121650285</v>
       </c>
       <c r="B3" t="n">
-        <v>57535</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593438</v>
+        <v>593479</v>
       </c>
       <c r="R3" t="n">
-        <v>6722918</v>
+        <v>6722986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +900,7 @@
         <v>121650410</v>
       </c>
       <c r="B4" t="n">
-        <v>57535</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650410</v>
+        <v>121650414</v>
       </c>
       <c r="B2" t="n">
         <v>57536</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593477</v>
+        <v>593438</v>
       </c>
       <c r="R2" t="n">
-        <v>6723107</v>
+        <v>6722918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650414</v>
+        <v>121650285</v>
       </c>
       <c r="B3" t="n">
         <v>57536</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593438</v>
+        <v>593479</v>
       </c>
       <c r="R3" t="n">
-        <v>6722918</v>
+        <v>6722986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650285</v>
+        <v>121650410</v>
       </c>
       <c r="B4" t="n">
         <v>57536</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593479</v>
+        <v>593477</v>
       </c>
       <c r="R4" t="n">
-        <v>6722986</v>
+        <v>6723107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650414</v>
+        <v>121650285</v>
       </c>
       <c r="B2" t="n">
         <v>57536</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593438</v>
+        <v>593479</v>
       </c>
       <c r="R2" t="n">
-        <v>6722918</v>
+        <v>6722986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650285</v>
+        <v>121650410</v>
       </c>
       <c r="B3" t="n">
         <v>57536</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593479</v>
+        <v>593477</v>
       </c>
       <c r="R3" t="n">
-        <v>6722986</v>
+        <v>6723107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650410</v>
+        <v>121650414</v>
       </c>
       <c r="B4" t="n">
         <v>57536</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593477</v>
+        <v>593438</v>
       </c>
       <c r="R4" t="n">
-        <v>6723107</v>
+        <v>6722918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650285</v>
+        <v>121650410</v>
       </c>
       <c r="B2" t="n">
         <v>57536</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593479</v>
+        <v>593477</v>
       </c>
       <c r="R2" t="n">
-        <v>6722986</v>
+        <v>6723107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650410</v>
+        <v>121650285</v>
       </c>
       <c r="B3" t="n">
         <v>57536</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593477</v>
+        <v>593479</v>
       </c>
       <c r="R3" t="n">
-        <v>6723107</v>
+        <v>6722986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650285</v>
+        <v>121650414</v>
       </c>
       <c r="B3" t="n">
         <v>57536</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593479</v>
+        <v>593438</v>
       </c>
       <c r="R3" t="n">
-        <v>6722986</v>
+        <v>6722918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650414</v>
+        <v>121650285</v>
       </c>
       <c r="B4" t="n">
         <v>57536</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593438</v>
+        <v>593479</v>
       </c>
       <c r="R4" t="n">
-        <v>6722918</v>
+        <v>6722986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650410</v>
+        <v>121650285</v>
       </c>
       <c r="B2" t="n">
         <v>57536</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593477</v>
+        <v>593479</v>
       </c>
       <c r="R2" t="n">
-        <v>6723107</v>
+        <v>6722986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650414</v>
+        <v>121650410</v>
       </c>
       <c r="B3" t="n">
         <v>57536</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593438</v>
+        <v>593477</v>
       </c>
       <c r="R3" t="n">
-        <v>6722918</v>
+        <v>6723107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650285</v>
+        <v>121650414</v>
       </c>
       <c r="B4" t="n">
         <v>57536</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593479</v>
+        <v>593438</v>
       </c>
       <c r="R4" t="n">
-        <v>6722986</v>
+        <v>6722918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650285</v>
+        <v>121650410</v>
       </c>
       <c r="B2" t="n">
         <v>57536</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593479</v>
+        <v>593477</v>
       </c>
       <c r="R2" t="n">
-        <v>6722986</v>
+        <v>6723107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650410</v>
+        <v>121650414</v>
       </c>
       <c r="B3" t="n">
         <v>57536</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593477</v>
+        <v>593438</v>
       </c>
       <c r="R3" t="n">
-        <v>6723107</v>
+        <v>6722918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650414</v>
+        <v>121650285</v>
       </c>
       <c r="B4" t="n">
         <v>57536</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593438</v>
+        <v>593479</v>
       </c>
       <c r="R4" t="n">
-        <v>6722918</v>
+        <v>6722986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650410</v>
+        <v>121650414</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57544</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593477</v>
+        <v>593438</v>
       </c>
       <c r="R2" t="n">
-        <v>6723107</v>
+        <v>6722918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650414</v>
+        <v>121650285</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57544</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593438</v>
+        <v>593479</v>
       </c>
       <c r="R3" t="n">
-        <v>6722918</v>
+        <v>6722986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650285</v>
+        <v>121650410</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57544</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593479</v>
+        <v>593477</v>
       </c>
       <c r="R4" t="n">
-        <v>6722986</v>
+        <v>6723107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>121650285</v>
       </c>
       <c r="B2" t="n">
-        <v>57544</v>
+        <v>57553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -789,11 +789,11 @@
         <v>121650414</v>
       </c>
       <c r="B3" t="n">
-        <v>57544</v>
+        <v>57553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -900,11 +900,11 @@
         <v>121650410</v>
       </c>
       <c r="B4" t="n">
-        <v>57544</v>
+        <v>57553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121650285</v>
       </c>
       <c r="B2" t="n">
-        <v>57553</v>
+        <v>57558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121650414</v>
       </c>
       <c r="B3" t="n">
-        <v>57553</v>
+        <v>57558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>121650410</v>
       </c>
       <c r="B4" t="n">
-        <v>57553</v>
+        <v>57558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 59065-2020 artfynd.xlsx
+++ b/artfynd/A 59065-2020 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>121650285</v>
       </c>
       <c r="B2" t="n">
-        <v>57558</v>
+        <v>57544</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -789,11 +789,11 @@
         <v>121650414</v>
       </c>
       <c r="B3" t="n">
-        <v>57558</v>
+        <v>57544</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -900,11 +900,11 @@
         <v>121650410</v>
       </c>
       <c r="B4" t="n">
-        <v>57558</v>
+        <v>57544</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
